--- a/results/02_taxa_assemblage/LDA_Method/ModelD_AllSites/artifacts/site_robustness.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelD_AllSites/artifacts/site_robustness.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -498,19 +498,19 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6384879248459042</v>
+        <v>0.8227129320187038</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1739826282617904</v>
+        <v>0.1623350272647026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1875294468923054</v>
+        <v>0.01495204071659373</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6384879248459042</v>
+        <v>0.8227129320187038</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4509584779535989</v>
+        <v>0.6603779047540013</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -533,22 +533,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3112264453207559</v>
+        <v>0.6129708958425141</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1682933998774564</v>
+        <v>0.007924216525737812</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5204801548017877</v>
+        <v>0.379104887631748</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5204801548017877</v>
+        <v>0.6129708958425141</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2092537094810317</v>
+        <v>0.233866008210766</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -563,30 +563,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1892992924075861</v>
+        <v>0.5536331807636843</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2990299027992622</v>
+        <v>0.02290953803865976</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5116708047931517</v>
+        <v>0.423457281197656</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5116708047931517</v>
+        <v>0.5536331807636843</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2126409019938895</v>
+        <v>0.1301758995660283</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -612,19 +612,19 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.674116740685579</v>
+        <v>0.8825683527426665</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04820158995541508</v>
+        <v>0.001780913972690638</v>
       </c>
       <c r="G5" t="n">
-        <v>0.277681669359006</v>
+        <v>0.115650733284643</v>
       </c>
       <c r="H5" t="n">
-        <v>0.674116740685579</v>
+        <v>0.8825683527426665</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3964350713265731</v>
+        <v>0.7669176194580236</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -643,26 +643,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09767866355239159</v>
+        <v>0.2624656867237872</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7009190641321115</v>
+        <v>0.7048429393262503</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2014022723154968</v>
+        <v>0.03269137394996238</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7009190641321115</v>
+        <v>0.7048429393262503</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4995167918166146</v>
+        <v>0.4423772526024631</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0358968710647238</v>
+        <v>0.01547013031270625</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8889383248752611</v>
+        <v>0.9839439585413281</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07516480406001511</v>
+        <v>0.0005859111459658408</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8889383248752611</v>
+        <v>0.9839439585413281</v>
       </c>
       <c r="I7" t="n">
-        <v>0.813773520815246</v>
+        <v>0.9684738282286218</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.182675569973357</v>
+        <v>0.6046651201831108</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5560694062179565</v>
+        <v>0.325596542889718</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2612550238086864</v>
+        <v>0.06973833692717113</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5560694062179565</v>
+        <v>0.6046651201831108</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2948143824092701</v>
+        <v>0.2790685772933928</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -764,19 +764,19 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006471497180066376</v>
+        <v>0.0007442660167040936</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9503449498424292</v>
+        <v>0.9992345840373095</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04318355297750433</v>
+        <v>2.114994598640313e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9503449498424292</v>
+        <v>0.9992345840373095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9071613968649249</v>
+        <v>0.9984903180206054</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -802,19 +802,19 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1153910511008272</v>
+        <v>0.4646380920169607</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6101061355013283</v>
+        <v>0.486140293245839</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2745028133978445</v>
+        <v>0.04922161473720031</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6101061355013283</v>
+        <v>0.486140293245839</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3356033221034838</v>
+        <v>0.0215022012288783</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -837,22 +837,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2953283891231361</v>
+        <v>0.5283138273795802</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4891133941625968</v>
+        <v>0.4503513834219831</v>
       </c>
       <c r="G11" t="n">
-        <v>0.215558216714267</v>
+        <v>0.0213347891984367</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4891133941625968</v>
+        <v>0.5283138273795802</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1937850050394607</v>
+        <v>0.07796244395759711</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1796342589591191</v>
+        <v>0.1115547177099446</v>
       </c>
       <c r="F12" t="n">
-        <v>0.697259804360873</v>
+        <v>0.8855711441225489</v>
       </c>
       <c r="G12" t="n">
-        <v>0.123105936680008</v>
+        <v>0.002874138167506471</v>
       </c>
       <c r="H12" t="n">
-        <v>0.697259804360873</v>
+        <v>0.8855711441225489</v>
       </c>
       <c r="I12" t="n">
-        <v>0.517625545401754</v>
+        <v>0.7740164264126044</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -905,30 +905,30 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1854628571455957</v>
+        <v>0.9672004512860461</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01386488503336992</v>
+        <v>0.0019463491863558</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8006722578210343</v>
+        <v>0.03085319952759788</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8006722578210343</v>
+        <v>0.9672004512860461</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6152094006754386</v>
+        <v>0.9363472517584482</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -943,30 +943,30 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2622465962770164</v>
+        <v>0.7519386911556382</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03870669878005091</v>
+        <v>0.001382452696857181</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6990467049429328</v>
+        <v>0.2466788561475045</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6990467049429328</v>
+        <v>0.7519386911556382</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4368001086659163</v>
+        <v>0.5052598350081337</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,22 +989,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1696275770871306</v>
+        <v>0.678793884502875</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3648326004242026</v>
+        <v>0.1084848722611316</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4655398224886668</v>
+        <v>0.2127212432359934</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4655398224886668</v>
+        <v>0.678793884502875</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1007072220644642</v>
+        <v>0.4660726412668816</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0.009986848046944156</v>
+        <v>0.01194508683554225</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9284118365317481</v>
+        <v>0.9803261166292183</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0616013154213078</v>
+        <v>0.007728796535239535</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9284118365317481</v>
+        <v>0.9803261166292183</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8668105211104403</v>
+        <v>0.968381029793676</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1061,26 +1061,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06827304032142881</v>
+        <v>0.2448207906296095</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7228997644337616</v>
+        <v>0.6328973812967928</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2088271952448096</v>
+        <v>0.1222818280735977</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7228997644337616</v>
+        <v>0.6328973812967928</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5140725691889521</v>
+        <v>0.3880765906671834</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1106,19 +1106,19 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2415836974197565</v>
+        <v>0.06280483963954589</v>
       </c>
       <c r="F18" t="n">
-        <v>0.592955756057696</v>
+        <v>0.9364790873937788</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1654605465225474</v>
+        <v>0.0007160729666752705</v>
       </c>
       <c r="H18" t="n">
-        <v>0.592955756057696</v>
+        <v>0.9364790873937788</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3513720586379395</v>
+        <v>0.873674247754233</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1144,19 +1144,19 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5612498753895986</v>
+        <v>0.8750811751479771</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09847732495102154</v>
+        <v>0.006903882856491353</v>
       </c>
       <c r="G19" t="n">
-        <v>0.34027279965938</v>
+        <v>0.1180149419955315</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5612498753895986</v>
+        <v>0.8750811751479771</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2209770757302186</v>
+        <v>0.7570662331524456</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1175,26 +1175,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7256305351620561</v>
+        <v>0.9795513441674608</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05333957446937902</v>
+        <v>0.01121315415421329</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2210298903685647</v>
+        <v>0.009235501678325861</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7256305351620561</v>
+        <v>0.9795513441674608</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5046006447934914</v>
+        <v>0.9683381900132475</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1220,19 +1220,19 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7364982617406779</v>
+        <v>0.9463662662894782</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07360682503814307</v>
+        <v>0.01733924860391048</v>
       </c>
       <c r="G21" t="n">
-        <v>0.189894913221179</v>
+        <v>0.03629448510661133</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7364982617406779</v>
+        <v>0.9463662662894782</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5466033485194989</v>
+        <v>0.9100717811828668</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1258,19 +1258,19 @@
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2162717749509419</v>
+        <v>0.2773584935458888</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5960408572679219</v>
+        <v>0.7123062140873121</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1876873677811362</v>
+        <v>0.01033529236679901</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5960408572679219</v>
+        <v>0.7123062140873121</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3797690823169799</v>
+        <v>0.4349477205414233</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1285,30 +1285,30 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3431598086007459</v>
+        <v>0.7242614723669388</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1527264307831744</v>
+        <v>0.01900349434357728</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5041137606160797</v>
+        <v>0.2567350332894838</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5041137606160797</v>
+        <v>0.7242614723669388</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1609539520153338</v>
+        <v>0.4675264390774551</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1327,26 +1327,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4916493911403892</v>
+        <v>0.8339232447460777</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06255918924147336</v>
+        <v>0.003107974693626344</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4457914196181375</v>
+        <v>0.162968780560296</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4916493911403892</v>
+        <v>0.8339232447460777</v>
       </c>
       <c r="I24" t="n">
-        <v>0.04585797152225179</v>
+        <v>0.6709544641857816</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1365,26 +1365,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2328332722470612</v>
+        <v>0.0722848661571882</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03601312816602621</v>
+        <v>6.436013548294972e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7311535995869126</v>
+        <v>0.9277086978292636</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7311535995869126</v>
+        <v>0.9277086978292636</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4983203273398514</v>
+        <v>0.8554238316720754</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1399,30 +1399,30 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2894701871471663</v>
+        <v>0.5605475946799989</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2890500447056115</v>
+        <v>0.02125578689356071</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4214797681472222</v>
+        <v>0.4181966184264402</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4214797681472222</v>
+        <v>0.5605475946799989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1320095810000559</v>
+        <v>0.1423509762535587</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1441,26 +1441,26 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6128641379995503</v>
+        <v>0.8740420051741592</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05283042104280592</v>
+        <v>0.002556188625283781</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3343054409576436</v>
+        <v>0.1234018062005571</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6128641379995503</v>
+        <v>0.8740420051741592</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2785586970419067</v>
+        <v>0.7506401989736021</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1479,26 +1479,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3867979835115963</v>
+        <v>0.8189261199768897</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1632683708898723</v>
+        <v>0.0199507167639406</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4499336455985314</v>
+        <v>0.1611231632591696</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4499336455985314</v>
+        <v>0.8189261199768897</v>
       </c>
       <c r="I28" t="n">
-        <v>0.06313566208693511</v>
+        <v>0.65780295671772</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1517,26 +1517,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.305245640508688</v>
+        <v>0.7105160249011201</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3588695887495945</v>
+        <v>0.2413511836273542</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3358847707417176</v>
+        <v>0.04813279147152577</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3588695887495945</v>
+        <v>0.7105160249011201</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02298481800787694</v>
+        <v>0.4691648412737659</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1562,19 +1562,19 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6065018470900148</v>
+        <v>0.8492084126901156</v>
       </c>
       <c r="F30" t="n">
-        <v>0.06678210444281854</v>
+        <v>0.004033581040453188</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3267160484671667</v>
+        <v>0.1467580062694312</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6065018470900148</v>
+        <v>0.8492084126901156</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2797857986228481</v>
+        <v>0.7024504064206845</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1593,26 +1593,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5726529810803053</v>
+        <v>0.9233157543238026</v>
       </c>
       <c r="F31" t="n">
-        <v>0.04013940096349326</v>
+        <v>0.002186808104682802</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3872076179562016</v>
+        <v>0.07449743757151452</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5726529810803053</v>
+        <v>0.9233157543238026</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1854453631241037</v>
+        <v>0.8488183167522881</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6705799784544841</v>
+        <v>0.9293806480318986</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05186728140016237</v>
+        <v>0.003918558007820381</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2775527401453535</v>
+        <v>0.066700793960281</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6705799784544841</v>
+        <v>0.9293806480318986</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3930272383091306</v>
+        <v>0.8626798540716176</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1669,26 +1669,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8412942447441585</v>
+        <v>0.9889889475983021</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01256402915167709</v>
+        <v>0.001544257679236183</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1461417261041645</v>
+        <v>0.009466794722461765</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8412942447441585</v>
+        <v>0.9889889475983021</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6951525186399939</v>
+        <v>0.9795221528758403</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1703,30 +1703,30 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5586567073409155</v>
+        <v>0.6617105086455741</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01861540368729267</v>
+        <v>6.916191803318334e-05</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4227278889717918</v>
+        <v>0.3382203294363927</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5586567073409155</v>
+        <v>0.6617105086455741</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1359288183691238</v>
+        <v>0.3234901792091814</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1752,19 +1752,19 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5187929713515627</v>
+        <v>0.7614846173365277</v>
       </c>
       <c r="F35" t="n">
-        <v>0.03911244333341766</v>
+        <v>0.0007169627561372377</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4420945853150197</v>
+        <v>0.2377984199073349</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5187929713515627</v>
+        <v>0.7614846173365277</v>
       </c>
       <c r="I35" t="n">
-        <v>0.07669838603654294</v>
+        <v>0.5236861974291928</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1790,19 +1790,19 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.558542179409953</v>
+        <v>0.7906824795801507</v>
       </c>
       <c r="F36" t="n">
-        <v>0.04531677858107239</v>
+        <v>0.001138389266837371</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3961410420089747</v>
+        <v>0.2081791311530121</v>
       </c>
       <c r="H36" t="n">
-        <v>0.558542179409953</v>
+        <v>0.7906824795801507</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1624011374009783</v>
+        <v>0.5825033484271386</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1828,19 +1828,19 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6154915761681782</v>
+        <v>0.7610490343108718</v>
       </c>
       <c r="F37" t="n">
-        <v>0.04590503169629671</v>
+        <v>0.0009772794960368563</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3386033921355253</v>
+        <v>0.2379736861930913</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6154915761681782</v>
+        <v>0.7610490343108718</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2768881840326529</v>
+        <v>0.5230753481177804</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1866,19 +1866,19 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5089012382987126</v>
+        <v>0.6813339686754368</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0658222297857529</v>
+        <v>0.001125223644552299</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4252765319155345</v>
+        <v>0.3175408076800109</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5089012382987126</v>
+        <v>0.6813339686754368</v>
       </c>
       <c r="I38" t="n">
-        <v>0.08362470638317809</v>
+        <v>0.3637931609954259</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1901,22 +1901,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4263124378496773</v>
+        <v>0.8160574137745711</v>
       </c>
       <c r="F39" t="n">
-        <v>0.06501219796232791</v>
+        <v>0.002854108648743742</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5086753641879949</v>
+        <v>0.1810884775766851</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5086753641879949</v>
+        <v>0.8160574137745711</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0823629263383176</v>
+        <v>0.634968936197886</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1942,19 +1942,19 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6345865042120974</v>
+        <v>0.7788570599166156</v>
       </c>
       <c r="F40" t="n">
-        <v>0.04191367224506003</v>
+        <v>0.000912299021831178</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3234998235428426</v>
+        <v>0.2202306410615532</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6345865042120974</v>
+        <v>0.7788570599166156</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3110866806692548</v>
+        <v>0.5586264188550624</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1969,30 +1969,30 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3431177564016146</v>
+        <v>0.6416699039359487</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2105057975309531</v>
+        <v>0.01226352699465541</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4463764460674323</v>
+        <v>0.3460665690693958</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4463764460674323</v>
+        <v>0.6416699039359487</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1032586896658177</v>
+        <v>0.2956033348665529</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2018,19 +2018,19 @@
         <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4472512560357609</v>
+        <v>0.4213686807418734</v>
       </c>
       <c r="F42" t="n">
-        <v>0.06379588843548709</v>
+        <v>0.00035958189604182</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4889528555287521</v>
+        <v>0.5782717373620848</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4889528555287521</v>
+        <v>0.5782717373620848</v>
       </c>
       <c r="I42" t="n">
-        <v>0.04170159949299124</v>
+        <v>0.1569030566202114</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2045,30 +2045,30 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3542878050112805</v>
+        <v>0.5849315774174422</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1926379824009698</v>
+        <v>0.006753255048133702</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4530742125877495</v>
+        <v>0.408315167534424</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4530742125877495</v>
+        <v>0.5849315774174422</v>
       </c>
       <c r="I43" t="n">
-        <v>0.098786407576469</v>
+        <v>0.1766164098830181</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2094,19 +2094,19 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5930284309417544</v>
+        <v>0.7632160020263108</v>
       </c>
       <c r="F44" t="n">
-        <v>0.05176909350988981</v>
+        <v>0.001170480857491865</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3552024755483558</v>
+        <v>0.2356135171161974</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5930284309417544</v>
+        <v>0.7632160020263108</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2378259553933986</v>
+        <v>0.5276024849101134</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2132,19 +2132,19 @@
         <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3397801524176692</v>
+        <v>0.4908406402849497</v>
       </c>
       <c r="F45" t="n">
-        <v>0.04562090222138183</v>
+        <v>0.0003588567950621011</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6145989453609489</v>
+        <v>0.5088005029199881</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6145989453609489</v>
+        <v>0.5088005029199881</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2748187929432797</v>
+        <v>0.0179598626350384</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2163,26 +2163,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2724548225033185</v>
+        <v>0.612355141564926</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3040835499275376</v>
+        <v>0.03571541515252499</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4234616275691441</v>
+        <v>0.351929443282549</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4234616275691441</v>
+        <v>0.612355141564926</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1193780776416065</v>
+        <v>0.260425698282377</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2197,30 +2197,30 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2395513880410126</v>
+        <v>0.4796008917494105</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2317862001190339</v>
+        <v>0.01383634322685028</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5286624118399534</v>
+        <v>0.5065627650237393</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5286624118399534</v>
+        <v>0.5065627650237393</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2891110237989409</v>
+        <v>0.02696187327432886</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2235,30 +2235,30 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3194921086450393</v>
+        <v>0.7323560663777257</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1907875604830443</v>
+        <v>0.01473788996965416</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4897203308719164</v>
+        <v>0.2529060436526202</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4897203308719164</v>
+        <v>0.7323560663777257</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1702282222268771</v>
+        <v>0.4794500227251055</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2284,19 +2284,19 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4385422989353268</v>
+        <v>0.8453290686545697</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1874568489154467</v>
+        <v>0.03002275195771519</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3740008521492265</v>
+        <v>0.1246481793877152</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4385422989353268</v>
+        <v>0.8453290686545697</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0645414467861003</v>
+        <v>0.7206808892668545</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2322,19 +2322,19 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5277771637937906</v>
+        <v>0.8025060433442937</v>
       </c>
       <c r="F50" t="n">
-        <v>0.07931892867206107</v>
+        <v>0.003239987729851916</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3929039075341484</v>
+        <v>0.1942539689258544</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5277771637937906</v>
+        <v>0.8025060433442937</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1348732562596421</v>
+        <v>0.6082520744184392</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2360,19 +2360,19 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4288493550672653</v>
+        <v>0.6742366583403903</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3162086902483491</v>
+        <v>0.275571149586696</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2549419546843856</v>
+        <v>0.0501921920729138</v>
       </c>
       <c r="H51" t="n">
-        <v>0.4288493550672653</v>
+        <v>0.6742366583403903</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1126406648189163</v>
+        <v>0.3986655087536942</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
